--- a/stories/arbres/TREE-SAN-007.xlsx
+++ b/stories/arbres/TREE-SAN-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, la maison devient calme. Sara bâille. Maman dit : c'est l'heure. Papa ouvre le lit. On met le pyjama. Puis c'est le dodo. Le corps a besoin de dormir.</t>
+          <t>Le soir, la maison devient calme. Sara bâille. C'est l'heure. Papa ouvre le lit. On met le pyjama. Puis c'est le dodo. Le corps a besoin de dormir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, la maison devient calme. Sara bâille.
+maman|C'est l'heure. Papa ouvre le lit. On met le pyjama.
+narrateur|Puis c'est le dodo. Le corps a besoin de dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Le chat en peluche attend sur l'oreiller. Le soir, Sara met son pyjama. Il est doux. Maman dit : au lit. Sara se couche. C'est le dodo. Papa baisse la lumière.</t>
+          <t>Le chat en peluche attend sur l'oreiller. Le soir, Sara met son pyjama. Il est doux. Au lit. Sara se couche. C'est le dodo. Papa baisse la lumière.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat en peluche attend sur l'oreiller. Le soir, Sara met son pyjama. Il est doux.
+maman|Au lit.
+narrateur|Sara se couche. C'est le dodo. Papa baisse la lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va dormir. Que met-elle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a le pyjama. Le soir, elle est au lit. C'est le dodo. Le chat peluche est là.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2227,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara pense au bac à sable. Les mains sont lavées. Le soir, elle a le pyjama. Elle se couche. Dodo. Le chat peluche ronronne, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2589,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le pyjama rouge est chaud. Le soir, Sara est au dodo. Le chat peluche aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Le pyjama bleu est doux. Sara a mis le pyjama. Le soir, dodo. Une étoile à la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le pyjama vert a des étoiles. Sara se couche. Le soir, dodo. Le bac à sable est loin.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient du toboggan. Les jambes sont fatiguées. Le soir, pyjama. Au lit. Dodo. Maman pose le chat peluche.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3953,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4122,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Sara est au dodo. Le soir. Le chat peluche veille. Papa chuchote.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4289,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4456,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Papa chuchote une histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4623,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4790,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. Sara ferme les yeux. Le soir, dodo. Le toboggan se tait.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara pense aux balançoires. Ça va, ça vient. Maintenant, le soir. Pyjama. Dodo. Le chat peluche est sous le bras.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5317,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5486,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Sara respire. Le soir, dodo. Le chat peluche est sous le bras.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5653,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5820,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, au lit. Dodo. Les balançoires sont loin.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5987,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6154,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. Le chat peluche est là. Sara, dodo. Le soir. Maman baisse la lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6321,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6350,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Le chien en peluche a de grandes oreilles. Le soir, Sara met son pyjama. Papa l'aide. Elle se couche. C'est le dodo. Maman dit : le corps a besoin de dormir.</t>
+          <t>Le chien en peluche a de grandes oreilles. Le soir, Sara met son pyjama. Papa l'aide. Elle se couche. C'est le dodo. Le corps a besoin de dormir.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6488,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien en peluche a de grandes oreilles. Le soir, Sara met son pyjama. Papa l'aide. Elle se couche. C'est le dodo.
+maman|Le corps a besoin de dormir.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6674,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Sara met le pyjama. Puis elle va où ?</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6847,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien peluche est au pied du lit. Sara a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6853,6 +7040,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
     </row>
@@ -7017,6 +7209,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Sara a creusé. Maintenant les mains sont propres. Le soir, pyjama. Dodo. Le chien peluche garde.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7205,6 +7402,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7369,6 +7571,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Sara est au dodo. Le soir. Le chien peluche aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7738,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7905,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Le chien peluche a de grandes oreilles.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8072,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8239,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. Sara se couche. Le soir, dodo. Le sable est lavé des mains.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8406,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8573,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a glissé au toboggan. Les jambes sont lourdes. Le soir, elle a le pyjama. Au lit. Dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8529,6 +8766,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8693,6 +8935,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Dodo. Le soir. Le chien peluche est chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9102,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9269,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Papa baisse le store.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9436,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9603,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. Sara ferme les yeux. Le soir, dodo. Les jambes sont lourdes.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9770,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9937,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Les balançoires sont loin, maintenant. Le soir, pyjama. Sara se couche. Dodo. Le chien peluche a une oreille sur l'oreiller.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9853,6 +10130,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10017,6 +10299,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Sara, dodo. Le soir. Une oreille de chien peluche sur l'oreiller.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10466,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10633,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, au lit. Dodo. Plus de balançoire.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10800,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10967,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. Le chien peluche veille. Sara, dodo. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11134,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10989,6 +11301,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|La poule en peluche est ronde et douce. Le soir, Sara met son pyjama. Maman boutonne. Sara se couche. C'est le dodo. Papa raconte deux phrases. Puis silence.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11482,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a la poule peluche. Que met-elle pour dormir ?</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11655,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La poule peluche est sous le coude. Sara a le pyjama. Le soir, dodo.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11521,6 +11848,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
     </row>
@@ -11685,6 +12017,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Le bac à sable est fermé. Le soir, Sara a le pyjama. Elle se couche. Dodo. La poule peluche est là.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11873,6 +12210,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12037,6 +12379,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Sara, dodo. Le soir. La poule peluche est ronde.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12546,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12713,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. La poule peluche sous le coude.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12880,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13047,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. La poule peluche est ronde. Sara, dodo. Le soir. Le bac est fermé.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13214,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13381,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Plus de toboggan. Les pieds sont au lit. Le soir, pyjama. Dodo. Maman pose un baiser.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13197,6 +13574,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13361,6 +13743,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Sara est au dodo. Le soir. Maman pose un baiser.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13910,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14077,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Les pieds sont au lit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14244,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14411,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. Sara ferme les yeux. Le soir, dodo. Plus de toboggan.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14578,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14745,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Les balançoires se taisent dans sa tête. Le soir, Sara a le pyjama. Au lit. Dodo. La poule peluche reste.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14521,6 +14938,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14685,6 +15107,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama rouge. Dodo. Le soir. Les balançoires se taisent.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15274,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15441,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, au lit. Dodo. Papa raconte deux phrases.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15608,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15775,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Pyjama vert. La poule peluche est là. Sara, dodo. Le soir. Silence.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15942,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15607,6 +16059,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-007.xlsx
+++ b/stories/arbres/TREE-SAN-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Puis c'est le dodo. Le corps a besoin de dormir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1696,7 @@
 narrateur|Sara se couche. C'est le dodo. Papa baisse la lumière.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1880,7 @@
           <t>narrateur|Sara va dormir. Que met-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
           <t>narrateur|Sara a le pyjama. Le soir, elle est au lit. C'est le dodo. Le chat peluche est là.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2248,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2416,7 @@
           <t>narrateur|Sara pense au bac à sable. Les mains sont lavées. Le soir, elle a le pyjama. Elle se couche. Dodo. Le chat peluche ronronne, tout doux.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2612,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2780,7 @@
           <t>narrateur|Le pyjama rouge est chaud. Le soir, Sara est au dodo. Le chat peluche aussi.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3116,7 @@
           <t>narrateur|Le pyjama bleu est doux. Sara a mis le pyjama. Le soir, dodo. Une étoile à la fenêtre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3452,7 @@
           <t>narrateur|Le pyjama vert a des étoiles. Sara se couche. Le soir, dodo. Le bac à sable est loin.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3788,7 @@
           <t>narrateur|Sara se souvient du toboggan. Les jambes sont fatiguées. Le soir, pyjama. Au lit. Dodo. Maman pose le chat peluche.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3960,6 +3984,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4127,6 +4152,7 @@
           <t>narrateur|Pyjama rouge. Sara est au dodo. Le soir. Le chat peluche veille. Papa chuchote.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4294,6 +4320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4461,6 +4488,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Papa chuchote une histoire.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4628,6 +4656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4824,7 @@
           <t>narrateur|Pyjama vert. Sara ferme les yeux. Le soir, dodo. Le toboggan se tait.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +4992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5160,7 @@
           <t>narrateur|Sara pense aux balançoires. Ça va, ça vient. Maintenant, le soir. Pyjama. Dodo. Le chat peluche est sous le bras.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5324,6 +5356,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5491,6 +5524,7 @@
           <t>narrateur|Pyjama rouge. Sara respire. Le soir, dodo. Le chat peluche est sous le bras.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5658,6 +5692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5825,6 +5860,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, au lit. Dodo. Les balançoires sont loin.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5992,6 +6028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6159,6 +6196,7 @@
           <t>narrateur|Pyjama vert. Le chat peluche est là. Sara, dodo. Le soir. Maman baisse la lumière.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6326,6 +6364,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6494,6 +6533,11 @@
 maman|Le corps a besoin de dormir.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6681,6 +6725,7 @@
           <t>narrateur|Sara met le pyjama. Puis elle va où ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6852,6 +6897,11 @@
           <t>narrateur|Le chien peluche est au pied du lit. Sara a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7047,6 +7097,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7214,6 +7265,11 @@
           <t>narrateur|Au bac, Sara a creusé. Maintenant les mains sont propres. Le soir, pyjama. Dodo. Le chien peluche garde.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7409,6 +7465,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7576,6 +7633,11 @@
           <t>narrateur|Pyjama rouge. Sara est au dodo. Le soir. Le chien peluche aussi.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7743,6 +7805,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7910,6 +7973,11 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Le chien peluche a de grandes oreilles.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8077,6 +8145,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8244,6 +8313,7 @@
           <t>narrateur|Pyjama vert. Sara se couche. Le soir, dodo. Le sable est lavé des mains.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8411,6 +8481,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8578,6 +8649,7 @@
           <t>narrateur|Sara a glissé au toboggan. Les jambes sont lourdes. Le soir, elle a le pyjama. Au lit. Dodo.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8773,6 +8845,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8940,6 +9013,11 @@
           <t>narrateur|Pyjama rouge. Dodo. Le soir. Le chien peluche est chaud.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9107,6 +9185,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9274,6 +9353,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Papa baisse le store.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9441,6 +9521,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9608,6 +9689,7 @@
           <t>narrateur|Pyjama vert. Sara ferme les yeux. Le soir, dodo. Les jambes sont lourdes.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9775,6 +9857,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9942,6 +10025,11 @@
           <t>narrateur|Les balançoires sont loin, maintenant. Le soir, pyjama. Sara se couche. Dodo. Le chien peluche a une oreille sur l'oreiller.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10137,6 +10225,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10304,6 +10393,11 @@
           <t>narrateur|Pyjama rouge. Sara, dodo. Le soir. Une oreille de chien peluche sur l'oreiller.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10471,6 +10565,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10638,6 +10733,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, au lit. Dodo. Plus de balançoire.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10805,6 +10901,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10972,6 +11069,11 @@
           <t>narrateur|Pyjama vert. Le chien peluche veille. Sara, dodo. Le soir.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11139,6 +11241,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11306,6 +11409,7 @@
           <t>narrateur|La poule en peluche est ronde et douce. Le soir, Sara met son pyjama. Maman boutonne. Sara se couche. C'est le dodo. Papa raconte deux phrases. Puis silence.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11489,6 +11593,7 @@
           <t>narrateur|Sara a la poule peluche. Que met-elle pour dormir ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11660,6 +11765,7 @@
           <t>narrateur|La poule peluche est sous le coude. Sara a le pyjama. Le soir, dodo.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11855,6 +11961,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12022,6 +12129,7 @@
           <t>narrateur|Le bac à sable est fermé. Le soir, Sara a le pyjama. Elle se couche. Dodo. La poule peluche est là.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12217,6 +12325,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12384,6 +12493,7 @@
           <t>narrateur|Pyjama rouge. Sara, dodo. Le soir. La poule peluche est ronde.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12551,6 +12661,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12718,6 +12829,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. La poule peluche sous le coude.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12885,6 +12997,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13052,6 +13165,7 @@
           <t>narrateur|Pyjama vert. La poule peluche est ronde. Sara, dodo. Le soir. Le bac est fermé.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13219,6 +13333,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13386,6 +13501,7 @@
           <t>narrateur|Plus de toboggan. Les pieds sont au lit. Le soir, pyjama. Dodo. Maman pose un baiser.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13581,6 +13697,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13748,6 +13865,7 @@
           <t>narrateur|Pyjama rouge. Sara est au dodo. Le soir. Maman pose un baiser.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13915,6 +14033,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14082,6 +14201,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, dodo. Les pieds sont au lit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14249,6 +14369,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14416,6 +14537,7 @@
           <t>narrateur|Pyjama vert. Sara ferme les yeux. Le soir, dodo. Plus de toboggan.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14583,6 +14705,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14750,6 +14873,7 @@
           <t>narrateur|Les balançoires se taisent dans sa tête. Le soir, Sara a le pyjama. Au lit. Dodo. La poule peluche reste.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14945,6 +15069,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15112,6 +15237,7 @@
           <t>narrateur|Pyjama rouge. Dodo. Le soir. Les balançoires se taisent.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15279,6 +15405,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15446,6 +15573,7 @@
           <t>narrateur|Pyjama bleu. Sara a mis le pyjama. Le soir, au lit. Dodo. Papa raconte deux phrases.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15613,6 +15741,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15780,6 +15909,7 @@
           <t>narrateur|Pyjama vert. La poule peluche est là. Sara, dodo. Le soir. Silence.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15947,6 +16077,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15965,7 +16096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16066,6 +16197,20 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16267,6 +16412,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
